--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:18</t>
+    <t xml:space="preserve">2026-09-09 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:13</t>
+    <t xml:space="preserve">2026-09-17 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:09</t>
+    <t xml:space="preserve">2026-09-23 12:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:38</t>
+    <t xml:space="preserve">2026-10-02 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:28</t>
+    <t xml:space="preserve">2026-10-04 09:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:06</t>
+    <t xml:space="preserve">2026-10-05 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -593,7 +593,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>325579.62</v>
+        <v>325579.63</v>
       </c>
     </row>
     <row r="8">
